--- a/powerbi-kit/files/data/asmis_sample.xlsx
+++ b/powerbi-kit/files/data/asmis_sample.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS151"/>
+  <dimension ref="A1:AW151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,6 +653,26 @@
           <t>Summary</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>SUB DATE REPORTED</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -692,7 +712,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -834,6 +854,19 @@
       <c r="AS2" t="inlineStr">
         <is>
           <t>SM strained a shoulder while lifting equipment cases into a trailer without assistance. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="n">
+        <v>45569</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -1022,6 +1055,19 @@
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT3" s="2" t="n">
+        <v>45567</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1205,6 +1251,19 @@
           <t>Full-time employee cut a finger on sheet metal while repairing a storage rack. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT4" s="2" t="n">
+        <v>45573</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1391,6 +1450,19 @@
           <t>Employee in a GSA vehicle clipped a mirror on a fuel island bollard. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT5" s="2" t="n">
+        <v>45578</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1574,6 +1646,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT6" s="2" t="n">
+        <v>45588</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1760,6 +1845,19 @@
           <t>Combat vehicle struck an embankment during night driver training; vehicle damaged, crew uninjured. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT7" s="2" t="n">
+        <v>45594</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1943,6 +2041,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT8" s="2" t="n">
+        <v>45631</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2126,6 +2237,19 @@
           <t>SM rolled an ankle on uneven ground during the two-mile run portion of a fitness test and was placed on profile. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT9" s="2" t="n">
+        <v>45634</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2312,6 +2436,19 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT10" s="2" t="n">
+        <v>45639</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2498,6 +2635,19 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT11" s="2" t="n">
+        <v>45641</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2681,6 +2831,19 @@
           <t>SM rolled an ankle on uneven ground during the two-mile run portion of a fitness test and was placed on profile. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT12" s="2" t="n">
+        <v>45646</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2864,6 +3027,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT13" s="2" t="n">
+        <v>45646</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3047,6 +3223,19 @@
           <t>Full-time employee cut a finger on sheet metal while repairing a storage rack. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT14" s="2" t="n">
+        <v>45648</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3233,6 +3422,19 @@
           <t>While backing a light tactical vehicle into the motor pool without a ground guide, the driver struck a parked trailer, damaging the rear bumper and trailer tongue. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT15" s="2" t="n">
+        <v>45653</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3416,6 +3618,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT16" s="2" t="n">
+        <v>45654</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3455,7 +3670,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3597,6 +3812,19 @@
       <c r="AS17" t="inlineStr">
         <is>
           <t>SM tripped over an extension cord in the supply cage and struck a knee on a shelf. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT17" s="2" t="n">
+        <v>45660</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -3782,6 +4010,19 @@
           <t>During organized PT, SM strained the lower back while performing deadlifts without a proper warm-up. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT18" s="2" t="n">
+        <v>45662</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3821,7 +4062,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3963,6 +4204,19 @@
       <c r="AS19" t="inlineStr">
         <is>
           <t>SM slipped on an icy sidewalk outside the readiness center before first formation and fractured a wrist. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT19" s="2" t="n">
+        <v>45663</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -4151,6 +4405,19 @@
           <t>Equipment fell from a pallet during forklift operations; property damage only. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT20" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4337,6 +4604,19 @@
           <t>GSA vehicle was struck in a parking lot while unattended at a readiness center. No injuries. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT21" s="2" t="n">
+        <v>45671</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4523,6 +4803,19 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT22" s="2" t="n">
+        <v>45674</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4706,6 +4999,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT23" s="2" t="n">
+        <v>45678</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4892,6 +5198,19 @@
           <t>During convoy movement to the training area, a cargo truck slid on gravel at a turn and entered the ditch. Minor injuries to the assistant driver. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT24" s="2" t="n">
+        <v>45680</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5075,6 +5394,19 @@
           <t>SM tripped over an extension cord in the supply cage and struck a knee on a shelf. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT25" s="2" t="n">
+        <v>45685</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5258,6 +5590,19 @@
           <t>SM strained a shoulder while lifting equipment cases into a trailer without assistance. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT26" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5441,6 +5786,19 @@
           <t>During annual training, SM showed signs of heat exhaustion during a ruck march and was evaluated by medics. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT27" s="2" t="n">
+        <v>45687</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5627,6 +5985,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT28" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5813,6 +6184,19 @@
           <t>During scheduled maintenance, a tool left in an access panel caused minor damage on engine run-up. No injuries. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT29" s="2" t="n">
+        <v>45693</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5999,6 +6383,19 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT30" s="2" t="n">
+        <v>45699</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6185,6 +6582,19 @@
           <t>During gunnery preparation, a track tensioning procedure was performed without the required tool and the crew member's hand was pinched. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT31" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6368,6 +6778,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT32" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6554,6 +6977,19 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT33" s="2" t="n">
+        <v>45705</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6593,7 +7029,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R - NG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -6738,6 +7174,19 @@
       <c r="AS34" t="inlineStr">
         <is>
           <t>Equipment fell from a pallet during forklift operations; property damage only. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT34" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -6926,6 +7375,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT35" s="2" t="n">
+        <v>45714</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7109,6 +7571,19 @@
           <t>GSA vehicle was struck in a parking lot while unattended at a readiness center. No injuries. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT36" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7292,6 +7767,19 @@
           <t>During organized PT, SM strained the lower back while performing deadlifts without a proper warm-up. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT37" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7478,6 +7966,19 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT38" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7664,6 +8165,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT39" s="2" t="n">
+        <v>45726</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7850,6 +8364,19 @@
           <t>Weather damage to a storage container door when a strong wind gust caught it during inventory. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT40" s="2" t="n">
+        <v>45732</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8036,6 +8563,19 @@
           <t>Weather damage to a storage container door when a strong wind gust caught it during inventory. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT41" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8222,6 +8762,19 @@
           <t>Ground handling of an aircraft into the hangar resulted in a rotor blade tip contacting a hangar door. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT42" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8405,6 +8958,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT43" s="2" t="n">
+        <v>45746</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8591,6 +9157,24 @@
           <t>Equipment fell from a pallet during forklift operations; property damage only. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT44" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>Witness statements pending</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>Unit requested extension</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8777,6 +9361,19 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT45" s="2" t="n">
+        <v>45750</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8963,6 +9560,19 @@
           <t>During gunnery preparation, a track tensioning procedure was performed without the required tool and the crew member's hand was pinched. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT46" s="2" t="n">
+        <v>45749</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9146,6 +9756,19 @@
           <t>Full-time employee cut a finger on sheet metal while repairing a storage rack. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT47" s="2" t="n">
+        <v>45756</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9329,6 +9952,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT48" s="2" t="n">
+        <v>45754</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9512,6 +10148,19 @@
           <t>SM slipped on an icy sidewalk outside the readiness center before first formation and fractured a wrist. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT49" s="2" t="n">
+        <v>45758</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9695,6 +10344,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT50" s="2" t="n">
+        <v>45789</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9734,7 +10396,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -9841,10 +10503,10 @@
         </is>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>42363</v>
+        <v>14566</v>
       </c>
       <c r="AL51" s="3" t="n">
-        <v>42363</v>
+        <v>14566</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
@@ -9879,6 +10541,19 @@
       <c r="AS51" t="inlineStr">
         <is>
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT51" s="2" t="n">
+        <v>45802</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -10064,6 +10739,19 @@
           <t>SM strained a shoulder while lifting equipment cases into a trailer without assistance. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT52" s="2" t="n">
+        <v>45802</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10250,6 +10938,19 @@
           <t>During convoy movement to the training area, a cargo truck slid on gravel at a turn and entered the ditch. Minor injuries to the assistant driver. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT53" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10433,6 +11134,19 @@
           <t>Full-time employee cut a finger on sheet metal while repairing a storage rack. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT54" s="2" t="n">
+        <v>45816</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10616,6 +11330,19 @@
           <t>SM slipped on an icy sidewalk outside the readiness center before first formation and fractured a wrist. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT55" s="2" t="n">
+        <v>45814</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10799,6 +11526,19 @@
           <t>During annual training, SM showed signs of heat exhaustion during a ruck march and was evaluated by medics. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT56" s="2" t="n">
+        <v>45821</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10985,6 +11725,19 @@
           <t>During convoy movement to the training area, a cargo truck slid on gravel at a turn and entered the ditch. Minor injuries to the assistant driver. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT57" s="2" t="n">
+        <v>45824</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11024,7 +11777,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -11131,10 +11884,10 @@
         </is>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>51957</v>
+        <v>12895</v>
       </c>
       <c r="AL58" s="3" t="n">
-        <v>51957</v>
+        <v>12895</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
@@ -11169,6 +11922,19 @@
       <c r="AS58" t="inlineStr">
         <is>
           <t>Combat vehicle struck an embankment during night driver training; vehicle damaged, crew uninjured. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT58" s="2" t="n">
+        <v>45828</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11976,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R - NG</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -11355,6 +12121,19 @@
       <c r="AS59" t="inlineStr">
         <is>
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT59" s="2" t="n">
+        <v>45833</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -11543,6 +12322,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT60" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -11729,6 +12521,19 @@
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT61" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11912,6 +12717,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT62" s="2" t="n">
+        <v>45837</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12098,6 +12916,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT63" s="2" t="n">
+        <v>45848</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12137,7 +12968,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -12279,6 +13110,19 @@
       <c r="AS64" t="inlineStr">
         <is>
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT64" s="2" t="n">
+        <v>45848</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
         </is>
       </c>
     </row>
@@ -12467,6 +13311,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT65" s="2" t="n">
+        <v>45852</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12653,6 +13510,19 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT66" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -12836,6 +13706,19 @@
           <t>During organized PT, SM strained the lower back while performing deadlifts without a proper warm-up. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT67" s="2" t="n">
+        <v>45857</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13022,6 +13905,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT68" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13208,6 +14104,19 @@
           <t>While backing a light tactical vehicle into the motor pool without a ground guide, the driver struck a parked trailer, damaging the rear bumper and trailer tongue. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT69" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13391,6 +14300,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT70" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13577,6 +14499,19 @@
           <t>During convoy movement to the training area, a cargo truck slid on gravel at a turn and entered the ditch. Minor injuries to the assistant driver. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT71" s="2" t="n">
+        <v>45864</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13763,6 +14698,19 @@
           <t>Combat vehicle struck an embankment during night driver training; vehicle damaged, crew uninjured. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT72" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13946,6 +14894,19 @@
           <t>Equipment fell from a pallet during forklift operations; property damage only. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT73" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -14129,6 +15090,19 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT74" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -14315,6 +15289,19 @@
           <t>During scheduled maintenance, a tool left in an access panel caused minor damage on engine run-up. No injuries. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT75" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14498,6 +15485,19 @@
           <t>SM strained a shoulder while lifting equipment cases into a trailer without assistance. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT76" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -14684,6 +15684,19 @@
           <t>Weather damage to a storage container door when a strong wind gust caught it during inventory. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT77" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -14867,6 +15880,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT78" s="2" t="n">
+        <v>45935</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -15053,6 +16079,19 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT79" s="2" t="n">
+        <v>45942</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15236,6 +16275,19 @@
           <t>During organized PT, SM strained the lower back while performing deadlifts without a proper warm-up. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT80" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15422,6 +16474,19 @@
           <t>During gunnery preparation, a track tensioning procedure was performed without the required tool and the crew member's hand was pinched. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT81" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15608,6 +16673,19 @@
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT82" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -15647,7 +16725,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -15754,10 +16832,10 @@
         </is>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>6051</v>
+        <v>21007</v>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>6051</v>
+        <v>21007</v>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
@@ -15792,6 +16870,19 @@
       <c r="AS83" t="inlineStr">
         <is>
           <t>During convoy movement to the training area, a cargo truck slid on gravel at a turn and entered the ditch. Minor injuries to the assistant driver. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT83" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -15833,7 +16924,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R - NG</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -15978,6 +17069,24 @@
       <c r="AS84" t="inlineStr">
         <is>
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT84" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -16166,6 +17275,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT85" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16205,7 +17327,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -16312,10 +17434,10 @@
         </is>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>53945</v>
+        <v>7512</v>
       </c>
       <c r="AL86" s="3" t="n">
-        <v>53945</v>
+        <v>7512</v>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
@@ -16350,6 +17472,19 @@
       <c r="AS86" t="inlineStr">
         <is>
           <t>GSA vehicle was struck in a parking lot while unattended at a readiness center. No injuries. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT86" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
         </is>
       </c>
     </row>
@@ -16535,6 +17670,19 @@
           <t>During organized PT, SM strained the lower back while performing deadlifts without a proper warm-up. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT87" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>Witness statements pending</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16718,6 +17866,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT88" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16904,6 +18065,19 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT89" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -16943,7 +18117,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R - NG</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -17088,6 +18262,19 @@
       <c r="AS90" t="inlineStr">
         <is>
           <t>Weather damage to a storage container door when a strong wind gust caught it during inventory. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT90" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
         </is>
       </c>
     </row>
@@ -17276,6 +18463,19 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT91" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17462,6 +18662,19 @@
           <t>Equipment fell from a pallet during forklift operations; property damage only. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT92" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17648,6 +18861,19 @@
           <t>While backing a light tactical vehicle into the motor pool without a ground guide, the driver struck a parked trailer, damaging the rear bumper and trailer tongue. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT93" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -17831,6 +19057,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT94" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18014,6 +19253,19 @@
           <t>SM slipped on an icy sidewalk outside the readiness center before first formation and fractured a wrist. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT95" s="2" t="n">
+        <v>46032</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18200,6 +19452,19 @@
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT96" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18383,6 +19648,19 @@
           <t>SM slipped on an icy sidewalk outside the readiness center before first formation and fractured a wrist. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT97" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -18569,6 +19847,14 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT98" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18755,6 +20041,19 @@
           <t>While backing a light tactical vehicle into the motor pool without a ground guide, the driver struck a parked trailer, damaging the rear bumper and trailer tongue. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT99" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -18794,7 +20093,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R - NG</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -18939,6 +20238,24 @@
       <c r="AS100" t="inlineStr">
         <is>
           <t>While backing a light tactical vehicle into the motor pool without a ground guide, the driver struck a parked trailer, damaging the rear bumper and trailer tongue. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT100" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>Returned for corrections</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
         </is>
       </c>
     </row>
@@ -19124,6 +20441,19 @@
           <t>SM rolled an ankle on uneven ground during the two-mile run portion of a fitness test and was placed on profile. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT101" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19310,6 +20640,19 @@
           <t>While backing a light tactical vehicle into the motor pool without a ground guide, the driver struck a parked trailer, damaging the rear bumper and trailer tongue. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT102" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19493,6 +20836,19 @@
           <t>SM strained a shoulder while lifting equipment cases into a trailer without assistance. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT103" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19532,7 +20888,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -19639,10 +20995,10 @@
         </is>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>26517</v>
+        <v>7400</v>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>26517</v>
+        <v>7400</v>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
@@ -19677,6 +21033,19 @@
       <c r="AS104" t="inlineStr">
         <is>
           <t>During scheduled maintenance, a tool left in an access panel caused minor damage on engine run-up. No injuries. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT104" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
         </is>
       </c>
     </row>
@@ -19862,6 +21231,19 @@
           <t>SM sustained a laceration while clearing brush during field training; treated and returned to duty. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT105" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20045,6 +21427,19 @@
           <t>Driver's hand was caught between the tailgate and bed while securing a load on a light tactical vehicle. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT106" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20231,6 +21626,19 @@
           <t>GSA vehicle was struck in a parking lot while unattended at a readiness center. No injuries. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT107" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20417,6 +21825,19 @@
           <t>While backing a light tactical vehicle into the motor pool without a ground guide, the driver struck a parked trailer, damaging the rear bumper and trailer tongue. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT108" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20600,6 +22021,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT109" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20786,6 +22220,19 @@
           <t>During convoy movement to the training area, a cargo truck slid on gravel at a turn and entered the ditch. Minor injuries to the assistant driver. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT110" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>Returned for corrections</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20969,6 +22416,14 @@
           <t>During organized PT, SM strained the lower back while performing deadlifts without a proper warm-up. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT111" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -21155,6 +22610,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT112" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -21341,6 +22809,19 @@
           <t>During gunnery preparation, a track tensioning procedure was performed without the required tool and the crew member's hand was pinched. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT113" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -21527,6 +23008,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT114" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -21713,6 +23207,19 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT115" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -21896,6 +23403,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT116" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -22079,6 +23599,24 @@
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT117" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -22262,6 +23800,24 @@
           <t>SM slipped on an icy sidewalk outside the readiness center before first formation and fractured a wrist. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT118" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>Witness statements pending</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>Awaiting cost data</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -22445,6 +24001,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT119" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -22631,6 +24200,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT120" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -22814,6 +24396,19 @@
           <t>SM tripped over an extension cord in the supply cage and struck a knee on a shelf. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT121" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -23000,6 +24595,19 @@
           <t>During gunnery preparation, a track tensioning procedure was performed without the required tool and the crew member's hand was pinched. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT122" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -23186,6 +24794,24 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT123" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>Awaiting cost data</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -23369,6 +24995,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT124" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -23555,6 +25194,19 @@
           <t>During scheduled maintenance, a tool left in an access panel caused minor damage on engine run-up. No injuries. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT125" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -23594,7 +25246,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E - grnd</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -23736,6 +25388,19 @@
       <c r="AS126" t="inlineStr">
         <is>
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT126" s="2" t="n">
+        <v>46207</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
@@ -23921,6 +25586,19 @@
           <t>SM strained a shoulder while lifting equipment cases into a trailer without assistance. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT127" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -24104,6 +25782,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT128" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>Awaiting cost data</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -24290,6 +25981,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT129" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>Abbreviated report on file</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -24473,6 +26177,19 @@
           <t>SM tripped over an extension cord in the supply cage and struck a knee on a shelf. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT130" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>Witness statements pending</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -24656,6 +26373,19 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT131" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -24842,6 +26572,24 @@
           <t>While traveling home after battle assembly, SM's privately owned vehicle left the roadway on a wet county road and struck a culvert. SM was transported to a local hospital and released. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT132" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -25028,6 +26776,19 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT133" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>Awaiting cost data</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -25214,6 +26975,19 @@
           <t>Equipment fell from a pallet during forklift operations; property damage only. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT134" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -25397,6 +27171,14 @@
           <t>Mechanic's finger was pinched between a hood and fender while closing the engine compartment. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT135" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -25583,6 +27365,19 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT136" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>Final report on file</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -25766,6 +27561,19 @@
           <t>During a services weekend, a jack stand shifted and a mechanic sustained a bruised forearm. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT137" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>Witness statements pending</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -25952,6 +27760,24 @@
           <t>Driver misjudged clearance while entering the wash rack and struck the overhead door frame. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT138" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>Returned for corrections</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -26135,6 +27961,24 @@
           <t>Full-time employee cut a finger on sheet metal while repairing a storage rack. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT139" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -26172,11 +28016,6 @@
           <t>1-627th Field Artillery Bn</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="I140" t="inlineStr">
         <is>
           <t>In Review NGB</t>
@@ -26319,6 +28158,19 @@
       <c r="AS140" t="inlineStr">
         <is>
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT140" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
         </is>
       </c>
     </row>
@@ -26504,6 +28356,24 @@
           <t>During the range day, SM received a minor burn from a hot casing; eye and skin protection reinforced. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT141" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Unit Safety Officer</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -26541,11 +28411,6 @@
           <t>2-512th Infantry Bn</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>In Review NGB</t>
@@ -26685,6 +28550,24 @@
       <c r="AS142" t="inlineStr">
         <is>
           <t>Equipment fell from a pallet during forklift operations; property damage only. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT142" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>Unit requested extension</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
         </is>
       </c>
     </row>
@@ -26724,11 +28607,6 @@
           <t>2-473rd Aviation Bn</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="I143" t="inlineStr">
         <is>
           <t>In Review NGB</t>
@@ -26871,6 +28749,24 @@
       <c r="AS143" t="inlineStr">
         <is>
           <t>SM's POV was rear-ended at a stoplight while driving to drill. SM reported neck pain and missed work for several days. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT143" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>Returned for corrections</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
         </is>
       </c>
     </row>
@@ -27059,6 +28955,24 @@
           <t>SM's POV struck a deer on a rural highway at dusk while returning from drill. No injuries; front-end damage. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT144" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>Returned for corrections</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -27096,11 +29010,6 @@
           <t>445th Cavalry Squadron</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="I145" t="inlineStr">
         <is>
           <t>Investigation Ongoing</t>
@@ -27243,6 +29152,19 @@
       <c r="AS145" t="inlineStr">
         <is>
           <t>GSA vehicle was struck in a parking lot while unattended at a readiness center. No injuries. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT145" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
         </is>
       </c>
     </row>
@@ -27428,6 +29350,19 @@
           <t>During annual training, SM showed signs of heat exhaustion during a ruck march and was evaluated by medics. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT146" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -27614,6 +29549,24 @@
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT147" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>Awaiting command endorsement</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>Unit requested extension</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -27797,6 +29750,19 @@
           <t>SM strained a shoulder while lifting equipment cases into a trailer without assistance. (Fictional record for demonstration.)</t>
         </is>
       </c>
+      <c r="AT148" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Occupational Health Technician</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -27834,11 +29800,6 @@
           <t>2-512th Infantry Bn</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="I149" t="inlineStr">
         <is>
           <t>Investigation Ongoing</t>
@@ -27978,6 +29939,24 @@
       <c r="AS149" t="inlineStr">
         <is>
           <t>During organized PT, SM strained the lower back while performing deadlifts without a proper warm-up. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT149" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
         </is>
       </c>
     </row>
@@ -28017,11 +29996,6 @@
           <t>2-473rd Aviation Bn</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="I150" t="inlineStr">
         <is>
           <t>Investigation Ongoing</t>
@@ -28161,6 +30135,24 @@
       <c r="AS150" t="inlineStr">
         <is>
           <t>SM sustained a laceration while clearing brush during field training; treated and returned to duty. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT150" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Draft report in progress</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>Pending medical update</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>State Safety Specialist</t>
         </is>
       </c>
     </row>
@@ -28200,11 +30192,6 @@
           <t>572nd Transportation Bn</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>Investigation Ongoing</t>
@@ -28344,6 +30331,24 @@
       <c r="AS151" t="inlineStr">
         <is>
           <t>During winter weather, SM lost control of a POV on an icy overpass and struck the guardrail. Vehicle damage only; SM uninjured. (Fictional record for demonstration.)</t>
+        </is>
+      </c>
+      <c r="AT151" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Witness statements pending</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>Returned for corrections</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Battalion Safety NCO</t>
         </is>
       </c>
     </row>
